--- a/artfynd/A 29679-2024 artfynd.xlsx
+++ b/artfynd/A 29679-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121589868</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 29679-2024 artfynd.xlsx
+++ b/artfynd/A 29679-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +782,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126400672</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80046</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sadimoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>727061</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7354929</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29679-2024 artfynd.xlsx
+++ b/artfynd/A 29679-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126400672</v>
       </c>
       <c r="B3" t="n">
-        <v>80046</v>
+        <v>80049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29679-2024 artfynd.xlsx
+++ b/artfynd/A 29679-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589868</v>
+        <v>121589870</v>
       </c>
       <c r="B2" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727102</v>
+        <v>726968</v>
       </c>
       <c r="R2" t="n">
-        <v>7354556</v>
+        <v>7354499</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,32 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126400672</v>
+        <v>126315540</v>
       </c>
       <c r="B3" t="n">
-        <v>80049</v>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229748</v>
+        <v>637</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -820,13 +815,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727061</v>
+        <v>726992</v>
       </c>
       <c r="R3" t="n">
-        <v>7354929</v>
+        <v>7355076</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,6 +874,313 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121589867</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>727076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7354484</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121589868</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jokkmokksmyran, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>727102</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7354556</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126400672</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sadimoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>727061</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7354929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29679-2024 artfynd.xlsx
+++ b/artfynd/A 29679-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126315540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589867</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121589868</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,8 +1206,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126400672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>